--- a/data/historico/semana_321.xlsx
+++ b/data/historico/semana_321.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$148</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$85</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$H$40</definedName>
   </definedNames>
@@ -5111,7 +5111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5123,7 +5123,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (7 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (8 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5155,12 +5155,12 @@
     <row r="3">
       <c r="A3" s="41" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="B3" s="41" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="C3" s="41" t="inlineStr">
@@ -5170,19 +5170,19 @@
       </c>
       <c r="D3" s="41" t="inlineStr">
         <is>
-          <t>Cicero Isrrael Sanabria</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="41" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="B4" s="41" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="C4" s="41" t="inlineStr">
@@ -5192,14 +5192,14 @@
       </c>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Ramona dos Santos Oliveira</t>
+          <t>Cicero Isrrael Sanabria</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="41" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="B5" s="41" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Mateus Falcao de Souza</t>
+          <t>Ramona dos Santos Oliveira</t>
         </is>
       </c>
     </row>
@@ -5236,51 +5236,51 @@
       </c>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Tania Maria Montania</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="41" t="inlineStr">
         <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="41" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="41" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D7" s="41" t="inlineStr">
+        <is>
+          <t>Tania Maria Montania</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="41" t="inlineStr">
+        <is>
           <t>20/08/2026</t>
         </is>
       </c>
-      <c r="B7" s="41" t="inlineStr">
+      <c r="B8" s="41" t="inlineStr">
         <is>
           <t>28/08/2026</t>
         </is>
       </c>
-      <c r="C7" s="41" t="inlineStr">
+      <c r="C8" s="41" t="inlineStr">
         <is>
           <t>Férias/Atestado (automático)</t>
         </is>
       </c>
-      <c r="D7" s="41" t="inlineStr">
+      <c r="D8" s="41" t="inlineStr">
         <is>
           <t>Alana Amanda Fernandes Ovelar</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="42" t="inlineStr">
-        <is>
-          <t>24/08/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="42" t="inlineStr">
-        <is>
-          <t>24/08/2026</t>
-        </is>
-      </c>
-      <c r="C8" s="42" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D8" s="42" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
         </is>
       </c>
     </row>
@@ -5302,12 +5302,34 @@
       </c>
       <c r="D9" s="42" t="inlineStr">
         <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="42" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="42" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="42" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D10" s="42" t="inlineStr">
+        <is>
           <t>Equipe 3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D9"/>
+  <autoFilter ref="A2:D10"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -5330,7 +5352,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
@@ -6731,7 +6753,7 @@
       </c>
       <c r="G48" s="45" t="inlineStr">
         <is>
-          <t>378 - 2 - R</t>
+          <t>239 - R</t>
         </is>
       </c>
       <c r="H48" s="45" t="inlineStr">
@@ -6919,7 +6941,7 @@
       </c>
       <c r="G52" s="45" t="inlineStr">
         <is>
-          <t>775 - 3 - TB</t>
+          <t>775 - 2 - R</t>
         </is>
       </c>
       <c r="H52" s="45" t="inlineStr">
@@ -25020,47 +25042,47 @@
     <row r="17">
       <c r="A17" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B17" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C17" s="30" t="inlineStr">
         <is>
-          <t>17197913</t>
+          <t>17195999</t>
         </is>
       </c>
       <c r="D17" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E17" s="29" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q050</t>
         </is>
       </c>
       <c r="F17" s="29" t="inlineStr">
         <is>
-          <t>Rua GENERAL OSORIO</t>
+          <t>Avenida COSTA E SILVA</t>
         </is>
       </c>
       <c r="G17" s="29" t="inlineStr">
         <is>
-          <t>1542 - R</t>
+          <t>843 - R</t>
         </is>
       </c>
       <c r="H17" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:32</t>
+          <t>28/08/2026 08:55</t>
         </is>
       </c>
       <c r="I17" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:52</t>
+          <t>28/08/2026 09:15</t>
         </is>
       </c>
       <c r="J17" s="29" t="n">
@@ -25220,47 +25242,47 @@
     <row r="21">
       <c r="A21" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B21" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C21" s="30" t="inlineStr">
         <is>
-          <t>17195999</t>
+          <t>17197913</t>
         </is>
       </c>
       <c r="D21" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E21" s="29" t="inlineStr">
         <is>
-          <t>Q050</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="F21" s="29" t="inlineStr">
         <is>
-          <t>Avenida COSTA E SILVA</t>
+          <t>Rua GENERAL OSORIO</t>
         </is>
       </c>
       <c r="G21" s="29" t="inlineStr">
         <is>
-          <t>843 - R</t>
+          <t>1542 - R</t>
         </is>
       </c>
       <c r="H21" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 08:55</t>
+          <t>28/08/2026 14:32</t>
         </is>
       </c>
       <c r="I21" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:15</t>
+          <t>28/08/2026 14:52</t>
         </is>
       </c>
       <c r="J21" s="29" t="n">
@@ -25380,7 +25402,7 @@
       </c>
       <c r="C24" s="30" t="inlineStr">
         <is>
-          <t>17197903</t>
+          <t>17197904</t>
         </is>
       </c>
       <c r="D24" s="29" t="inlineStr">
@@ -25400,17 +25422,17 @@
       </c>
       <c r="G24" s="29" t="inlineStr">
         <is>
-          <t>669 - R</t>
+          <t>645 - R</t>
         </is>
       </c>
       <c r="H24" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:41</t>
+          <t>28/08/2026 10:02</t>
         </is>
       </c>
       <c r="I24" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:59</t>
+          <t>28/08/2026 10:20</t>
         </is>
       </c>
       <c r="J24" s="29" t="n">
@@ -25520,47 +25542,47 @@
     <row r="27">
       <c r="A27" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B27" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
-          <t>17197904</t>
+          <t>17196006</t>
         </is>
       </c>
       <c r="D27" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E27" s="29" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q050</t>
         </is>
       </c>
       <c r="F27" s="29" t="inlineStr">
         <is>
-          <t>Rua BALTAZAR SALDANHA</t>
+          <t>Rua 01 DE MARÇO</t>
         </is>
       </c>
       <c r="G27" s="29" t="inlineStr">
         <is>
-          <t>645 - R</t>
+          <t>69 - 1 - OU</t>
         </is>
       </c>
       <c r="H27" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 10:02</t>
+          <t>28/08/2026 09:32</t>
         </is>
       </c>
       <c r="I27" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 10:20</t>
+          <t>28/08/2026 09:50</t>
         </is>
       </c>
       <c r="J27" s="29" t="n">
@@ -25580,7 +25602,7 @@
       </c>
       <c r="C28" s="30" t="inlineStr">
         <is>
-          <t>17197908</t>
+          <t>17197903</t>
         </is>
       </c>
       <c r="D28" s="29" t="inlineStr">
@@ -25595,22 +25617,22 @@
       </c>
       <c r="F28" s="29" t="inlineStr">
         <is>
-          <t>Rua GENERAL OSORIO</t>
+          <t>Rua BALTAZAR SALDANHA</t>
         </is>
       </c>
       <c r="G28" s="29" t="inlineStr">
         <is>
-          <t>1486 - R</t>
+          <t>669 - R</t>
         </is>
       </c>
       <c r="H28" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 13:55</t>
+          <t>28/08/2026 09:41</t>
         </is>
       </c>
       <c r="I28" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:13</t>
+          <t>28/08/2026 09:59</t>
         </is>
       </c>
       <c r="J28" s="29" t="n">
@@ -25620,47 +25642,47 @@
     <row r="29">
       <c r="A29" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B29" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>17196006</t>
+          <t>17197908</t>
         </is>
       </c>
       <c r="D29" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E29" s="29" t="inlineStr">
         <is>
-          <t>Q050</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="F29" s="29" t="inlineStr">
         <is>
-          <t>Rua 01 DE MARÇO</t>
+          <t>Rua GENERAL OSORIO</t>
         </is>
       </c>
       <c r="G29" s="29" t="inlineStr">
         <is>
-          <t>69 - 1 - OU</t>
+          <t>1486 - R</t>
         </is>
       </c>
       <c r="H29" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:32</t>
+          <t>28/08/2026 13:55</t>
         </is>
       </c>
       <c r="I29" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:50</t>
+          <t>28/08/2026 14:13</t>
         </is>
       </c>
       <c r="J29" s="29" t="n">
@@ -26270,7 +26292,7 @@
     <row r="42">
       <c r="A42" s="29" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="B42" s="29" t="inlineStr">
@@ -26280,37 +26302,37 @@
       </c>
       <c r="C42" s="30" t="inlineStr">
         <is>
-          <t>17130878</t>
+          <t>17170026</t>
         </is>
       </c>
       <c r="D42" s="29" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>446 - GUY VILELA</t>
         </is>
       </c>
       <c r="E42" s="29" t="inlineStr">
         <is>
-          <t>Q044</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="F42" s="29" t="inlineStr">
         <is>
-          <t>Rua BENJAMIN CONSTANT</t>
+          <t>Avenida TAMANDARE</t>
         </is>
       </c>
       <c r="G42" s="29" t="inlineStr">
         <is>
-          <t>512 - 1 - R</t>
+          <t>466 - R</t>
         </is>
       </c>
       <c r="H42" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 10:27</t>
+          <t>27/08/2026 14:46</t>
         </is>
       </c>
       <c r="I42" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 10:43</t>
+          <t>27/08/2026 15:02</t>
         </is>
       </c>
       <c r="J42" s="29" t="n">
@@ -26320,7 +26342,7 @@
     <row r="43">
       <c r="A43" s="29" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B43" s="29" t="inlineStr">
@@ -26330,37 +26352,37 @@
       </c>
       <c r="C43" s="30" t="inlineStr">
         <is>
-          <t>17170026</t>
+          <t>17130878</t>
         </is>
       </c>
       <c r="D43" s="29" t="inlineStr">
         <is>
-          <t>446 - GUY VILELA</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E43" s="29" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q044</t>
         </is>
       </c>
       <c r="F43" s="29" t="inlineStr">
         <is>
-          <t>Avenida TAMANDARE</t>
+          <t>Rua BENJAMIN CONSTANT</t>
         </is>
       </c>
       <c r="G43" s="29" t="inlineStr">
         <is>
-          <t>466 - R</t>
+          <t>512 - 1 - R</t>
         </is>
       </c>
       <c r="H43" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 14:46</t>
+          <t>25/08/2026 10:27</t>
         </is>
       </c>
       <c r="I43" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 15:02</t>
+          <t>25/08/2026 10:43</t>
         </is>
       </c>
       <c r="J43" s="29" t="n">
@@ -29403,7 +29425,7 @@
       </c>
       <c r="H53" s="32" t="inlineStr">
         <is>
-          <t>553 - R</t>
+          <t>496 - 2 - TB</t>
         </is>
       </c>
       <c r="I53" s="32" t="inlineStr">
@@ -33621,7 +33643,7 @@
       </c>
       <c r="H127" s="32" t="inlineStr">
         <is>
-          <t>396 - R</t>
+          <t>376 - R</t>
         </is>
       </c>
       <c r="I127" s="32" t="inlineStr">
@@ -34704,7 +34726,7 @@
       </c>
       <c r="H146" s="32" t="inlineStr">
         <is>
-          <t>180 - 7 - TB</t>
+          <t>240 - 1 - TB</t>
         </is>
       </c>
       <c r="I146" s="32" t="inlineStr">
@@ -36190,7 +36212,7 @@
       </c>
       <c r="G26" s="35" t="inlineStr">
         <is>
-          <t>553 - R</t>
+          <t>496 - 2 - TB</t>
         </is>
       </c>
       <c r="H26" s="35" t="inlineStr">
@@ -38352,7 +38374,7 @@
       </c>
       <c r="G72" s="35" t="inlineStr">
         <is>
-          <t>396 - R</t>
+          <t>376 - R</t>
         </is>
       </c>
       <c r="H72" s="35" t="inlineStr">
@@ -38869,7 +38891,7 @@
       </c>
       <c r="G83" s="35" t="inlineStr">
         <is>
-          <t>180 - 7 - TB</t>
+          <t>240 - 1 - TB</t>
         </is>
       </c>
       <c r="H83" s="35" t="inlineStr">

--- a/data/historico/semana_321.xlsx
+++ b/data/historico/semana_321.xlsx
@@ -2844,16 +2844,16 @@
         <v>13</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T20" s="6" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>71.05</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="V20" s="6" t="n">
         <v>4.38</v>
@@ -5919,16 +5919,16 @@
         <v>33</v>
       </c>
       <c r="D20" s="29" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E20" s="29" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="29" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G20" s="29" t="n">
-        <v>71.05</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="n"/>
@@ -6528,16 +6528,16 @@
         <v>4596</v>
       </c>
       <c r="D41" s="26" t="n">
-        <v>2607</v>
+        <v>2605</v>
       </c>
       <c r="E41" s="26" t="n">
         <v>8</v>
       </c>
       <c r="F41" s="26" t="n">
-        <v>7211</v>
+        <v>7209</v>
       </c>
       <c r="G41" s="26" t="n">
-        <v>36.26</v>
+        <v>36.25</v>
       </c>
       <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="n"/>
@@ -19919,13 +19919,13 @@
         <v>21.21</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L33" s="6" t="n">
         <v>1</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>71.05</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="N33" s="6" t="inlineStr">
         <is>
@@ -25042,47 +25042,47 @@
     <row r="17">
       <c r="A17" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B17" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C17" s="30" t="inlineStr">
         <is>
-          <t>17195999</t>
+          <t>17197913</t>
         </is>
       </c>
       <c r="D17" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E17" s="29" t="inlineStr">
         <is>
-          <t>Q050</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="F17" s="29" t="inlineStr">
         <is>
-          <t>Avenida COSTA E SILVA</t>
+          <t>Rua GENERAL OSORIO</t>
         </is>
       </c>
       <c r="G17" s="29" t="inlineStr">
         <is>
-          <t>843 - R</t>
+          <t>1542 - R</t>
         </is>
       </c>
       <c r="H17" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 08:55</t>
+          <t>28/08/2026 14:32</t>
         </is>
       </c>
       <c r="I17" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:15</t>
+          <t>28/08/2026 14:52</t>
         </is>
       </c>
       <c r="J17" s="29" t="n">
@@ -25242,47 +25242,47 @@
     <row r="21">
       <c r="A21" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B21" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C21" s="30" t="inlineStr">
         <is>
-          <t>17197913</t>
+          <t>17195999</t>
         </is>
       </c>
       <c r="D21" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E21" s="29" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q050</t>
         </is>
       </c>
       <c r="F21" s="29" t="inlineStr">
         <is>
-          <t>Rua GENERAL OSORIO</t>
+          <t>Avenida COSTA E SILVA</t>
         </is>
       </c>
       <c r="G21" s="29" t="inlineStr">
         <is>
-          <t>1542 - R</t>
+          <t>843 - R</t>
         </is>
       </c>
       <c r="H21" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:32</t>
+          <t>28/08/2026 08:55</t>
         </is>
       </c>
       <c r="I21" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:52</t>
+          <t>28/08/2026 09:15</t>
         </is>
       </c>
       <c r="J21" s="29" t="n">
@@ -25402,7 +25402,7 @@
       </c>
       <c r="C24" s="30" t="inlineStr">
         <is>
-          <t>17197904</t>
+          <t>17197903</t>
         </is>
       </c>
       <c r="D24" s="29" t="inlineStr">
@@ -25422,17 +25422,17 @@
       </c>
       <c r="G24" s="29" t="inlineStr">
         <is>
-          <t>645 - R</t>
+          <t>669 - R</t>
         </is>
       </c>
       <c r="H24" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 10:02</t>
+          <t>28/08/2026 09:41</t>
         </is>
       </c>
       <c r="I24" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 10:20</t>
+          <t>28/08/2026 09:59</t>
         </is>
       </c>
       <c r="J24" s="29" t="n">
@@ -25542,47 +25542,47 @@
     <row r="27">
       <c r="A27" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B27" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
-          <t>17196006</t>
+          <t>17197904</t>
         </is>
       </c>
       <c r="D27" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E27" s="29" t="inlineStr">
         <is>
-          <t>Q050</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="F27" s="29" t="inlineStr">
         <is>
-          <t>Rua 01 DE MARÇO</t>
+          <t>Rua BALTAZAR SALDANHA</t>
         </is>
       </c>
       <c r="G27" s="29" t="inlineStr">
         <is>
-          <t>69 - 1 - OU</t>
+          <t>645 - R</t>
         </is>
       </c>
       <c r="H27" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:32</t>
+          <t>28/08/2026 10:02</t>
         </is>
       </c>
       <c r="I27" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:50</t>
+          <t>28/08/2026 10:20</t>
         </is>
       </c>
       <c r="J27" s="29" t="n">
@@ -25602,7 +25602,7 @@
       </c>
       <c r="C28" s="30" t="inlineStr">
         <is>
-          <t>17197903</t>
+          <t>17197908</t>
         </is>
       </c>
       <c r="D28" s="29" t="inlineStr">
@@ -25617,22 +25617,22 @@
       </c>
       <c r="F28" s="29" t="inlineStr">
         <is>
-          <t>Rua BALTAZAR SALDANHA</t>
+          <t>Rua GENERAL OSORIO</t>
         </is>
       </c>
       <c r="G28" s="29" t="inlineStr">
         <is>
-          <t>669 - R</t>
+          <t>1486 - R</t>
         </is>
       </c>
       <c r="H28" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:41</t>
+          <t>28/08/2026 13:55</t>
         </is>
       </c>
       <c r="I28" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:59</t>
+          <t>28/08/2026 14:13</t>
         </is>
       </c>
       <c r="J28" s="29" t="n">
@@ -25642,47 +25642,47 @@
     <row r="29">
       <c r="A29" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B29" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>17197908</t>
+          <t>17196006</t>
         </is>
       </c>
       <c r="D29" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E29" s="29" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q050</t>
         </is>
       </c>
       <c r="F29" s="29" t="inlineStr">
         <is>
-          <t>Rua GENERAL OSORIO</t>
+          <t>Rua 01 DE MARÇO</t>
         </is>
       </c>
       <c r="G29" s="29" t="inlineStr">
         <is>
-          <t>1486 - R</t>
+          <t>69 - 1 - OU</t>
         </is>
       </c>
       <c r="H29" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 13:55</t>
+          <t>28/08/2026 09:32</t>
         </is>
       </c>
       <c r="I29" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:13</t>
+          <t>28/08/2026 09:50</t>
         </is>
       </c>
       <c r="J29" s="29" t="n">
@@ -26292,7 +26292,7 @@
     <row r="42">
       <c r="A42" s="29" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B42" s="29" t="inlineStr">
@@ -26302,37 +26302,37 @@
       </c>
       <c r="C42" s="30" t="inlineStr">
         <is>
-          <t>17170026</t>
+          <t>17130878</t>
         </is>
       </c>
       <c r="D42" s="29" t="inlineStr">
         <is>
-          <t>446 - GUY VILELA</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E42" s="29" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q044</t>
         </is>
       </c>
       <c r="F42" s="29" t="inlineStr">
         <is>
-          <t>Avenida TAMANDARE</t>
+          <t>Rua BENJAMIN CONSTANT</t>
         </is>
       </c>
       <c r="G42" s="29" t="inlineStr">
         <is>
-          <t>466 - R</t>
+          <t>512 - 1 - R</t>
         </is>
       </c>
       <c r="H42" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 14:46</t>
+          <t>25/08/2026 10:27</t>
         </is>
       </c>
       <c r="I42" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 15:02</t>
+          <t>25/08/2026 10:43</t>
         </is>
       </c>
       <c r="J42" s="29" t="n">
@@ -26342,7 +26342,7 @@
     <row r="43">
       <c r="A43" s="29" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="B43" s="29" t="inlineStr">
@@ -26352,37 +26352,37 @@
       </c>
       <c r="C43" s="30" t="inlineStr">
         <is>
-          <t>17130878</t>
+          <t>17170026</t>
         </is>
       </c>
       <c r="D43" s="29" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>446 - GUY VILELA</t>
         </is>
       </c>
       <c r="E43" s="29" t="inlineStr">
         <is>
-          <t>Q044</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="F43" s="29" t="inlineStr">
         <is>
-          <t>Rua BENJAMIN CONSTANT</t>
+          <t>Avenida TAMANDARE</t>
         </is>
       </c>
       <c r="G43" s="29" t="inlineStr">
         <is>
-          <t>512 - 1 - R</t>
+          <t>466 - R</t>
         </is>
       </c>
       <c r="H43" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 10:27</t>
+          <t>27/08/2026 14:46</t>
         </is>
       </c>
       <c r="I43" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 10:43</t>
+          <t>27/08/2026 15:02</t>
         </is>
       </c>
       <c r="J43" s="29" t="n">

--- a/data/historico/semana_321.xlsx
+++ b/data/historico/semana_321.xlsx
@@ -24692,47 +24692,47 @@
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="B10" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C10" s="30" t="inlineStr">
         <is>
-          <t>17148181</t>
+          <t>17131247</t>
         </is>
       </c>
       <c r="D10" s="29" t="inlineStr">
         <is>
-          <t>405 - ALTOS DA GLÓRIA</t>
+          <t>413 - BAIRRO DA GRANJA</t>
         </is>
       </c>
       <c r="E10" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="F10" s="29" t="inlineStr">
         <is>
-          <t>Rua ARNALDO VASQUES</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="G10" s="29" t="inlineStr">
         <is>
-          <t>325 - R</t>
+          <t>210 - C</t>
         </is>
       </c>
       <c r="H10" s="29" t="inlineStr">
         <is>
-          <t>26/08/2026 13:43</t>
+          <t>25/08/2026 08:43</t>
         </is>
       </c>
       <c r="I10" s="29" t="inlineStr">
         <is>
-          <t>26/08/2026 14:05</t>
+          <t>25/08/2026 09:05</t>
         </is>
       </c>
       <c r="J10" s="29" t="n">
@@ -24742,47 +24742,47 @@
     <row r="11">
       <c r="A11" s="29" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C11" s="30" t="inlineStr">
         <is>
-          <t>17131247</t>
+          <t>17148181</t>
         </is>
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F11" s="29" t="inlineStr">
         <is>
-          <t>Avenida BRASIL</t>
+          <t>Rua ARNALDO VASQUES</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
         <is>
-          <t>210 - C</t>
+          <t>325 - R</t>
         </is>
       </c>
       <c r="H11" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 08:43</t>
+          <t>26/08/2026 13:43</t>
         </is>
       </c>
       <c r="I11" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:05</t>
+          <t>26/08/2026 14:05</t>
         </is>
       </c>
       <c r="J11" s="29" t="n">
@@ -25042,47 +25042,47 @@
     <row r="17">
       <c r="A17" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="B17" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C17" s="30" t="inlineStr">
         <is>
-          <t>17197913</t>
+          <t>17153643</t>
         </is>
       </c>
       <c r="D17" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>402 - JARDIM MARAMBAIA</t>
         </is>
       </c>
       <c r="E17" s="29" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q032</t>
         </is>
       </c>
       <c r="F17" s="29" t="inlineStr">
         <is>
-          <t>Rua GENERAL OSORIO</t>
+          <t>Rua CORONEL ORLANDO SAPUCAIA</t>
         </is>
       </c>
       <c r="G17" s="29" t="inlineStr">
         <is>
-          <t>1542 - R</t>
+          <t>17 - R</t>
         </is>
       </c>
       <c r="H17" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:32</t>
+          <t>26/08/2026 14:07</t>
         </is>
       </c>
       <c r="I17" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:52</t>
+          <t>26/08/2026 14:27</t>
         </is>
       </c>
       <c r="J17" s="29" t="n">
@@ -25092,47 +25092,47 @@
     <row r="18">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B18" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C18" s="30" t="inlineStr">
         <is>
-          <t>17153643</t>
+          <t>17197913</t>
         </is>
       </c>
       <c r="D18" s="29" t="inlineStr">
         <is>
-          <t>402 - JARDIM MARAMBAIA</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E18" s="29" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="F18" s="29" t="inlineStr">
         <is>
-          <t>Rua CORONEL ORLANDO SAPUCAIA</t>
+          <t>Rua GENERAL OSORIO</t>
         </is>
       </c>
       <c r="G18" s="29" t="inlineStr">
         <is>
-          <t>17 - R</t>
+          <t>1542 - R</t>
         </is>
       </c>
       <c r="H18" s="29" t="inlineStr">
         <is>
-          <t>26/08/2026 14:07</t>
+          <t>28/08/2026 14:32</t>
         </is>
       </c>
       <c r="I18" s="29" t="inlineStr">
         <is>
-          <t>26/08/2026 14:27</t>
+          <t>28/08/2026 14:52</t>
         </is>
       </c>
       <c r="J18" s="29" t="n">
@@ -25392,47 +25392,47 @@
     <row r="24">
       <c r="A24" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B24" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C24" s="30" t="inlineStr">
         <is>
-          <t>17197903</t>
+          <t>17092097</t>
         </is>
       </c>
       <c r="D24" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="E24" s="29" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F24" s="29" t="inlineStr">
         <is>
-          <t>Rua BALTAZAR SALDANHA</t>
+          <t>Rua ARNALDO VASQUES</t>
         </is>
       </c>
       <c r="G24" s="29" t="inlineStr">
         <is>
-          <t>669 - R</t>
+          <t>347 - R</t>
         </is>
       </c>
       <c r="H24" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:41</t>
+          <t>24/08/2026 09:00</t>
         </is>
       </c>
       <c r="I24" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:59</t>
+          <t>24/08/2026 09:18</t>
         </is>
       </c>
       <c r="J24" s="29" t="n">
@@ -25492,47 +25492,47 @@
     <row r="26">
       <c r="A26" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B26" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C26" s="30" t="inlineStr">
         <is>
-          <t>17092097</t>
+          <t>17184336</t>
         </is>
       </c>
       <c r="D26" s="29" t="inlineStr">
         <is>
-          <t>405 - ALTOS DA GLÓRIA</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E26" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="F26" s="29" t="inlineStr">
         <is>
-          <t>Rua ARNALDO VASQUES</t>
+          <t>Rua GENERAL OSORIO</t>
         </is>
       </c>
       <c r="G26" s="29" t="inlineStr">
         <is>
-          <t>347 - R</t>
+          <t>1391 - R</t>
         </is>
       </c>
       <c r="H26" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:00</t>
+          <t>27/08/2026 13:23</t>
         </is>
       </c>
       <c r="I26" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:18</t>
+          <t>27/08/2026 13:41</t>
         </is>
       </c>
       <c r="J26" s="29" t="n">
@@ -25602,7 +25602,7 @@
       </c>
       <c r="C28" s="30" t="inlineStr">
         <is>
-          <t>17197908</t>
+          <t>17197903</t>
         </is>
       </c>
       <c r="D28" s="29" t="inlineStr">
@@ -25617,22 +25617,22 @@
       </c>
       <c r="F28" s="29" t="inlineStr">
         <is>
-          <t>Rua GENERAL OSORIO</t>
+          <t>Rua BALTAZAR SALDANHA</t>
         </is>
       </c>
       <c r="G28" s="29" t="inlineStr">
         <is>
-          <t>1486 - R</t>
+          <t>669 - R</t>
         </is>
       </c>
       <c r="H28" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 13:55</t>
+          <t>28/08/2026 09:41</t>
         </is>
       </c>
       <c r="I28" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:13</t>
+          <t>28/08/2026 09:59</t>
         </is>
       </c>
       <c r="J28" s="29" t="n">
@@ -25702,7 +25702,7 @@
       </c>
       <c r="C30" s="30" t="inlineStr">
         <is>
-          <t>17184336</t>
+          <t>17197908</t>
         </is>
       </c>
       <c r="D30" s="29" t="inlineStr">
@@ -25712,7 +25712,7 @@
       </c>
       <c r="E30" s="29" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="F30" s="29" t="inlineStr">
@@ -25722,17 +25722,17 @@
       </c>
       <c r="G30" s="29" t="inlineStr">
         <is>
-          <t>1391 - R</t>
+          <t>1486 - R</t>
         </is>
       </c>
       <c r="H30" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 13:23</t>
+          <t>28/08/2026 13:55</t>
         </is>
       </c>
       <c r="I30" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 13:41</t>
+          <t>28/08/2026 14:13</t>
         </is>
       </c>
       <c r="J30" s="29" t="n">
@@ -25752,7 +25752,7 @@
       </c>
       <c r="C31" s="30" t="inlineStr">
         <is>
-          <t>17197893</t>
+          <t>17184338</t>
         </is>
       </c>
       <c r="D31" s="29" t="inlineStr">
@@ -25762,27 +25762,27 @@
       </c>
       <c r="E31" s="29" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="F31" s="29" t="inlineStr">
         <is>
-          <t>Rua CALOGERAS</t>
+          <t>Rua GENERAL OSORIO</t>
         </is>
       </c>
       <c r="G31" s="29" t="inlineStr">
         <is>
-          <t>1493 - R</t>
+          <t>1353 - C</t>
         </is>
       </c>
       <c r="H31" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 08:17</t>
+          <t>27/08/2026 13:50</t>
         </is>
       </c>
       <c r="I31" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 08:34</t>
+          <t>27/08/2026 14:07</t>
         </is>
       </c>
       <c r="J31" s="29" t="n">
@@ -25792,7 +25792,7 @@
     <row r="32">
       <c r="A32" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B32" s="29" t="inlineStr">
@@ -25802,37 +25802,37 @@
       </c>
       <c r="C32" s="30" t="inlineStr">
         <is>
-          <t>17098963</t>
+          <t>17197893</t>
         </is>
       </c>
       <c r="D32" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E32" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="F32" s="29" t="inlineStr">
         <is>
-          <t>Rua ARINO MOREIRA</t>
+          <t>Rua CALOGERAS</t>
         </is>
       </c>
       <c r="G32" s="29" t="inlineStr">
         <is>
-          <t>39 - R</t>
+          <t>1493 - R</t>
         </is>
       </c>
       <c r="H32" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:46</t>
+          <t>28/08/2026 08:17</t>
         </is>
       </c>
       <c r="I32" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 16:03</t>
+          <t>28/08/2026 08:34</t>
         </is>
       </c>
       <c r="J32" s="29" t="n">
@@ -25842,7 +25842,7 @@
     <row r="33">
       <c r="A33" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Cicero Isrrael Sanabria</t>
         </is>
       </c>
       <c r="B33" s="29" t="inlineStr">
@@ -25852,37 +25852,37 @@
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>17195900</t>
+          <t>17133115</t>
         </is>
       </c>
       <c r="D33" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>412 - COHAB</t>
         </is>
       </c>
       <c r="E33" s="29" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="F33" s="29" t="inlineStr">
         <is>
-          <t>Rua 13 DE SETEMBRO</t>
+          <t>Rua VALENCIO DE BRUM</t>
         </is>
       </c>
       <c r="G33" s="29" t="inlineStr">
         <is>
-          <t>1502 - R</t>
+          <t>536 - R</t>
         </is>
       </c>
       <c r="H33" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:53</t>
+          <t>25/08/2026 09:33</t>
         </is>
       </c>
       <c r="I33" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 15:10</t>
+          <t>25/08/2026 09:50</t>
         </is>
       </c>
       <c r="J33" s="29" t="n">
@@ -25892,7 +25892,7 @@
     <row r="34">
       <c r="A34" s="29" t="inlineStr">
         <is>
-          <t>Cicero Isrrael Sanabria</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B34" s="29" t="inlineStr">
@@ -25902,37 +25902,37 @@
       </c>
       <c r="C34" s="30" t="inlineStr">
         <is>
-          <t>17133115</t>
+          <t>17098963</t>
         </is>
       </c>
       <c r="D34" s="29" t="inlineStr">
         <is>
-          <t>412 - COHAB</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E34" s="29" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F34" s="29" t="inlineStr">
         <is>
-          <t>Rua VALENCIO DE BRUM</t>
+          <t>Rua ARINO MOREIRA</t>
         </is>
       </c>
       <c r="G34" s="29" t="inlineStr">
         <is>
-          <t>536 - R</t>
+          <t>39 - R</t>
         </is>
       </c>
       <c r="H34" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:33</t>
+          <t>24/08/2026 15:46</t>
         </is>
       </c>
       <c r="I34" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:50</t>
+          <t>24/08/2026 16:03</t>
         </is>
       </c>
       <c r="J34" s="29" t="n">
@@ -25942,7 +25942,7 @@
     <row r="35">
       <c r="A35" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B35" s="29" t="inlineStr">
@@ -25952,37 +25952,37 @@
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>17184338</t>
+          <t>17195900</t>
         </is>
       </c>
       <c r="D35" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E35" s="29" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F35" s="29" t="inlineStr">
         <is>
-          <t>Rua GENERAL OSORIO</t>
+          <t>Rua 13 DE SETEMBRO</t>
         </is>
       </c>
       <c r="G35" s="29" t="inlineStr">
         <is>
-          <t>1353 - C</t>
+          <t>1502 - R</t>
         </is>
       </c>
       <c r="H35" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 13:50</t>
+          <t>28/08/2026 14:53</t>
         </is>
       </c>
       <c r="I35" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 14:07</t>
+          <t>28/08/2026 15:10</t>
         </is>
       </c>
       <c r="J35" s="29" t="n">
@@ -25992,47 +25992,47 @@
     <row r="36">
       <c r="A36" s="29" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B36" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C36" s="30" t="inlineStr">
         <is>
-          <t>17137370</t>
+          <t>17098958</t>
         </is>
       </c>
       <c r="D36" s="29" t="inlineStr">
         <is>
-          <t>402 - JARDIM MARAMBAIA</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E36" s="29" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F36" s="29" t="inlineStr">
         <is>
-          <t>Rua DR HELIO BRANDAO</t>
+          <t>Avenida COMANDANTE CARDOSO</t>
         </is>
       </c>
       <c r="G36" s="29" t="inlineStr">
         <is>
-          <t>647 - R</t>
+          <t>258 - 2 - OU</t>
         </is>
       </c>
       <c r="H36" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 16:03</t>
+          <t>24/08/2026 14:47</t>
         </is>
       </c>
       <c r="I36" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 16:19</t>
+          <t>24/08/2026 15:03</t>
         </is>
       </c>
       <c r="J36" s="29" t="n">
@@ -26192,47 +26192,47 @@
     <row r="40">
       <c r="A40" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="B40" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C40" s="30" t="inlineStr">
         <is>
-          <t>17098958</t>
+          <t>17137370</t>
         </is>
       </c>
       <c r="D40" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>402 - JARDIM MARAMBAIA</t>
         </is>
       </c>
       <c r="E40" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F40" s="29" t="inlineStr">
         <is>
-          <t>Avenida COMANDANTE CARDOSO</t>
+          <t>Rua DR HELIO BRANDAO</t>
         </is>
       </c>
       <c r="G40" s="29" t="inlineStr">
         <is>
-          <t>258 - 2 - OU</t>
+          <t>647 - R</t>
         </is>
       </c>
       <c r="H40" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 14:47</t>
+          <t>25/08/2026 16:03</t>
         </is>
       </c>
       <c r="I40" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:03</t>
+          <t>25/08/2026 16:19</t>
         </is>
       </c>
       <c r="J40" s="29" t="n">

--- a/data/historico/semana_321.xlsx
+++ b/data/historico/semana_321.xlsx
@@ -1647,16 +1647,16 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>5</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>31.8</v>
+        <v>32.4</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>4</v>
@@ -1665,7 +1665,7 @@
         <v>10</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>6.29</v>
+        <v>6.17</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>0</v>
@@ -1695,23 +1695,23 @@
         <v>0</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>34.57</v>
+        <v>34.15</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>5.41</v>
+        <v>5.43</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>27.03</v>
+        <v>27.17</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Y9" s="4" t="inlineStr">
         <is>
-          <t>R$ 83,41</t>
+          <t>R$ 81,97</t>
         </is>
       </c>
       <c r="Z9" s="4" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="AC9" s="4" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:22</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="C9" s="29" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D9" s="29" t="n">
         <v>84</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="G9" s="29" t="n">
-        <v>34.57</v>
+        <v>34.15</v>
       </c>
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="n"/>
@@ -6525,7 +6525,7 @@
         </is>
       </c>
       <c r="C41" s="26" t="n">
-        <v>4596</v>
+        <v>4599</v>
       </c>
       <c r="D41" s="26" t="n">
         <v>2605</v>
@@ -6534,10 +6534,10 @@
         <v>8</v>
       </c>
       <c r="F41" s="26" t="n">
-        <v>7209</v>
+        <v>7212</v>
       </c>
       <c r="G41" s="26" t="n">
-        <v>36.25</v>
+        <v>36.23</v>
       </c>
       <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="n"/>
@@ -18978,27 +18978,27 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>5.16</v>
+        <v>5.15</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>5</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Q014, Q015, Q016, Q017, Q018, Q024, Q025, Q026, Q027, Q028, Q029, Q030, Q031, Q032</t>
+          <t>Q013, Q014, Q015, Q016, Q017, Q018, Q024, Q025, Q026, Q027, Q028, Q029, Q030, Q031, Q032</t>
         </is>
       </c>
       <c r="I16" s="4" t="n">
         <v>8</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>60</v>
@@ -19007,7 +19007,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>32.43</v>
+        <v>31.91</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>

--- a/data/historico/semana_321.xlsx
+++ b/data/historico/semana_321.xlsx
@@ -24692,7 +24692,7 @@
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B10" s="29" t="inlineStr">
@@ -24702,37 +24702,37 @@
       </c>
       <c r="C10" s="30" t="inlineStr">
         <is>
-          <t>17131247</t>
+          <t>17130213</t>
         </is>
       </c>
       <c r="D10" s="29" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E10" s="29" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="F10" s="29" t="inlineStr">
         <is>
-          <t>Avenida BRASIL</t>
+          <t>Rua ROSA AZUL</t>
         </is>
       </c>
       <c r="G10" s="29" t="inlineStr">
         <is>
-          <t>210 - C</t>
+          <t>222 - R</t>
         </is>
       </c>
       <c r="H10" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 08:43</t>
+          <t>25/08/2026 15:33</t>
         </is>
       </c>
       <c r="I10" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:05</t>
+          <t>25/08/2026 15:55</t>
         </is>
       </c>
       <c r="J10" s="29" t="n">
@@ -24792,7 +24792,7 @@
     <row r="12">
       <c r="A12" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="B12" s="29" t="inlineStr">
@@ -24802,37 +24802,37 @@
       </c>
       <c r="C12" s="30" t="inlineStr">
         <is>
-          <t>17130213</t>
+          <t>17131247</t>
         </is>
       </c>
       <c r="D12" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>413 - BAIRRO DA GRANJA</t>
         </is>
       </c>
       <c r="E12" s="29" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="F12" s="29" t="inlineStr">
         <is>
-          <t>Rua ROSA AZUL</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="G12" s="29" t="inlineStr">
         <is>
-          <t>222 - R</t>
+          <t>210 - C</t>
         </is>
       </c>
       <c r="H12" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:33</t>
+          <t>25/08/2026 08:43</t>
         </is>
       </c>
       <c r="I12" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:55</t>
+          <t>25/08/2026 09:05</t>
         </is>
       </c>
       <c r="J12" s="29" t="n">

--- a/data/historico/semana_321.xlsx
+++ b/data/historico/semana_321.xlsx
@@ -24692,47 +24692,47 @@
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B10" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C10" s="30" t="inlineStr">
         <is>
-          <t>17130213</t>
+          <t>17148181</t>
         </is>
       </c>
       <c r="D10" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="E10" s="29" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F10" s="29" t="inlineStr">
         <is>
-          <t>Rua ROSA AZUL</t>
+          <t>Rua ARNALDO VASQUES</t>
         </is>
       </c>
       <c r="G10" s="29" t="inlineStr">
         <is>
-          <t>222 - R</t>
+          <t>325 - R</t>
         </is>
       </c>
       <c r="H10" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:33</t>
+          <t>26/08/2026 13:43</t>
         </is>
       </c>
       <c r="I10" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:55</t>
+          <t>26/08/2026 14:05</t>
         </is>
       </c>
       <c r="J10" s="29" t="n">
@@ -24742,47 +24742,47 @@
     <row r="11">
       <c r="A11" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C11" s="30" t="inlineStr">
         <is>
-          <t>17148181</t>
+          <t>17131247</t>
         </is>
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>405 - ALTOS DA GLÓRIA</t>
+          <t>413 - BAIRRO DA GRANJA</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="F11" s="29" t="inlineStr">
         <is>
-          <t>Rua ARNALDO VASQUES</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
         <is>
-          <t>325 - R</t>
+          <t>210 - C</t>
         </is>
       </c>
       <c r="H11" s="29" t="inlineStr">
         <is>
-          <t>26/08/2026 13:43</t>
+          <t>25/08/2026 08:43</t>
         </is>
       </c>
       <c r="I11" s="29" t="inlineStr">
         <is>
-          <t>26/08/2026 14:05</t>
+          <t>25/08/2026 09:05</t>
         </is>
       </c>
       <c r="J11" s="29" t="n">
@@ -24792,7 +24792,7 @@
     <row r="12">
       <c r="A12" s="29" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B12" s="29" t="inlineStr">
@@ -24802,37 +24802,37 @@
       </c>
       <c r="C12" s="30" t="inlineStr">
         <is>
-          <t>17131247</t>
+          <t>17130213</t>
         </is>
       </c>
       <c r="D12" s="29" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E12" s="29" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="F12" s="29" t="inlineStr">
         <is>
-          <t>Avenida BRASIL</t>
+          <t>Rua ROSA AZUL</t>
         </is>
       </c>
       <c r="G12" s="29" t="inlineStr">
         <is>
-          <t>210 - C</t>
+          <t>222 - R</t>
         </is>
       </c>
       <c r="H12" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 08:43</t>
+          <t>25/08/2026 15:33</t>
         </is>
       </c>
       <c r="I12" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:05</t>
+          <t>25/08/2026 15:55</t>
         </is>
       </c>
       <c r="J12" s="29" t="n">
@@ -25042,47 +25042,47 @@
     <row r="17">
       <c r="A17" s="29" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B17" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C17" s="30" t="inlineStr">
         <is>
-          <t>17153643</t>
+          <t>17197913</t>
         </is>
       </c>
       <c r="D17" s="29" t="inlineStr">
         <is>
-          <t>402 - JARDIM MARAMBAIA</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E17" s="29" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="F17" s="29" t="inlineStr">
         <is>
-          <t>Rua CORONEL ORLANDO SAPUCAIA</t>
+          <t>Rua GENERAL OSORIO</t>
         </is>
       </c>
       <c r="G17" s="29" t="inlineStr">
         <is>
-          <t>17 - R</t>
+          <t>1542 - R</t>
         </is>
       </c>
       <c r="H17" s="29" t="inlineStr">
         <is>
-          <t>26/08/2026 14:07</t>
+          <t>28/08/2026 14:32</t>
         </is>
       </c>
       <c r="I17" s="29" t="inlineStr">
         <is>
-          <t>26/08/2026 14:27</t>
+          <t>28/08/2026 14:52</t>
         </is>
       </c>
       <c r="J17" s="29" t="n">
@@ -25092,47 +25092,47 @@
     <row r="18">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="B18" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C18" s="30" t="inlineStr">
         <is>
-          <t>17197913</t>
+          <t>17153643</t>
         </is>
       </c>
       <c r="D18" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>402 - JARDIM MARAMBAIA</t>
         </is>
       </c>
       <c r="E18" s="29" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q032</t>
         </is>
       </c>
       <c r="F18" s="29" t="inlineStr">
         <is>
-          <t>Rua GENERAL OSORIO</t>
+          <t>Rua CORONEL ORLANDO SAPUCAIA</t>
         </is>
       </c>
       <c r="G18" s="29" t="inlineStr">
         <is>
-          <t>1542 - R</t>
+          <t>17 - R</t>
         </is>
       </c>
       <c r="H18" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:32</t>
+          <t>26/08/2026 14:07</t>
         </is>
       </c>
       <c r="I18" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:52</t>
+          <t>26/08/2026 14:27</t>
         </is>
       </c>
       <c r="J18" s="29" t="n">
@@ -25392,47 +25392,47 @@
     <row r="24">
       <c r="A24" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B24" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C24" s="30" t="inlineStr">
         <is>
-          <t>17092097</t>
+          <t>17197903</t>
         </is>
       </c>
       <c r="D24" s="29" t="inlineStr">
         <is>
-          <t>405 - ALTOS DA GLÓRIA</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E24" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="F24" s="29" t="inlineStr">
         <is>
-          <t>Rua ARNALDO VASQUES</t>
+          <t>Rua BALTAZAR SALDANHA</t>
         </is>
       </c>
       <c r="G24" s="29" t="inlineStr">
         <is>
-          <t>347 - R</t>
+          <t>669 - R</t>
         </is>
       </c>
       <c r="H24" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:00</t>
+          <t>28/08/2026 09:41</t>
         </is>
       </c>
       <c r="I24" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:18</t>
+          <t>28/08/2026 09:59</t>
         </is>
       </c>
       <c r="J24" s="29" t="n">
@@ -25492,47 +25492,47 @@
     <row r="26">
       <c r="A26" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B26" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C26" s="30" t="inlineStr">
         <is>
-          <t>17184336</t>
+          <t>17092097</t>
         </is>
       </c>
       <c r="D26" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="E26" s="29" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F26" s="29" t="inlineStr">
         <is>
-          <t>Rua GENERAL OSORIO</t>
+          <t>Rua ARNALDO VASQUES</t>
         </is>
       </c>
       <c r="G26" s="29" t="inlineStr">
         <is>
-          <t>1391 - R</t>
+          <t>347 - R</t>
         </is>
       </c>
       <c r="H26" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 13:23</t>
+          <t>24/08/2026 09:00</t>
         </is>
       </c>
       <c r="I26" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 13:41</t>
+          <t>24/08/2026 09:18</t>
         </is>
       </c>
       <c r="J26" s="29" t="n">
@@ -25602,7 +25602,7 @@
       </c>
       <c r="C28" s="30" t="inlineStr">
         <is>
-          <t>17197903</t>
+          <t>17197908</t>
         </is>
       </c>
       <c r="D28" s="29" t="inlineStr">
@@ -25617,22 +25617,22 @@
       </c>
       <c r="F28" s="29" t="inlineStr">
         <is>
-          <t>Rua BALTAZAR SALDANHA</t>
+          <t>Rua GENERAL OSORIO</t>
         </is>
       </c>
       <c r="G28" s="29" t="inlineStr">
         <is>
-          <t>669 - R</t>
+          <t>1486 - R</t>
         </is>
       </c>
       <c r="H28" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:41</t>
+          <t>28/08/2026 13:55</t>
         </is>
       </c>
       <c r="I28" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:59</t>
+          <t>28/08/2026 14:13</t>
         </is>
       </c>
       <c r="J28" s="29" t="n">
@@ -25702,7 +25702,7 @@
       </c>
       <c r="C30" s="30" t="inlineStr">
         <is>
-          <t>17197908</t>
+          <t>17184336</t>
         </is>
       </c>
       <c r="D30" s="29" t="inlineStr">
@@ -25712,7 +25712,7 @@
       </c>
       <c r="E30" s="29" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="F30" s="29" t="inlineStr">
@@ -25722,17 +25722,17 @@
       </c>
       <c r="G30" s="29" t="inlineStr">
         <is>
-          <t>1486 - R</t>
+          <t>1391 - R</t>
         </is>
       </c>
       <c r="H30" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 13:55</t>
+          <t>27/08/2026 13:23</t>
         </is>
       </c>
       <c r="I30" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:13</t>
+          <t>27/08/2026 13:41</t>
         </is>
       </c>
       <c r="J30" s="29" t="n">
@@ -25752,7 +25752,7 @@
       </c>
       <c r="C31" s="30" t="inlineStr">
         <is>
-          <t>17184338</t>
+          <t>17197893</t>
         </is>
       </c>
       <c r="D31" s="29" t="inlineStr">
@@ -25762,27 +25762,27 @@
       </c>
       <c r="E31" s="29" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="F31" s="29" t="inlineStr">
         <is>
-          <t>Rua GENERAL OSORIO</t>
+          <t>Rua CALOGERAS</t>
         </is>
       </c>
       <c r="G31" s="29" t="inlineStr">
         <is>
-          <t>1353 - C</t>
+          <t>1493 - R</t>
         </is>
       </c>
       <c r="H31" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 13:50</t>
+          <t>28/08/2026 08:17</t>
         </is>
       </c>
       <c r="I31" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 14:07</t>
+          <t>28/08/2026 08:34</t>
         </is>
       </c>
       <c r="J31" s="29" t="n">
@@ -25792,7 +25792,7 @@
     <row r="32">
       <c r="A32" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B32" s="29" t="inlineStr">
@@ -25802,37 +25802,37 @@
       </c>
       <c r="C32" s="30" t="inlineStr">
         <is>
-          <t>17197893</t>
+          <t>17098963</t>
         </is>
       </c>
       <c r="D32" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E32" s="29" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F32" s="29" t="inlineStr">
         <is>
-          <t>Rua CALOGERAS</t>
+          <t>Rua ARINO MOREIRA</t>
         </is>
       </c>
       <c r="G32" s="29" t="inlineStr">
         <is>
-          <t>1493 - R</t>
+          <t>39 - R</t>
         </is>
       </c>
       <c r="H32" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 08:17</t>
+          <t>24/08/2026 15:46</t>
         </is>
       </c>
       <c r="I32" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 08:34</t>
+          <t>24/08/2026 16:03</t>
         </is>
       </c>
       <c r="J32" s="29" t="n">
@@ -25842,7 +25842,7 @@
     <row r="33">
       <c r="A33" s="29" t="inlineStr">
         <is>
-          <t>Cicero Isrrael Sanabria</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B33" s="29" t="inlineStr">
@@ -25852,37 +25852,37 @@
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>17133115</t>
+          <t>17195900</t>
         </is>
       </c>
       <c r="D33" s="29" t="inlineStr">
         <is>
-          <t>412 - COHAB</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E33" s="29" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F33" s="29" t="inlineStr">
         <is>
-          <t>Rua VALENCIO DE BRUM</t>
+          <t>Rua 13 DE SETEMBRO</t>
         </is>
       </c>
       <c r="G33" s="29" t="inlineStr">
         <is>
-          <t>536 - R</t>
+          <t>1502 - R</t>
         </is>
       </c>
       <c r="H33" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:33</t>
+          <t>28/08/2026 14:53</t>
         </is>
       </c>
       <c r="I33" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:50</t>
+          <t>28/08/2026 15:10</t>
         </is>
       </c>
       <c r="J33" s="29" t="n">
@@ -25892,7 +25892,7 @@
     <row r="34">
       <c r="A34" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Cicero Isrrael Sanabria</t>
         </is>
       </c>
       <c r="B34" s="29" t="inlineStr">
@@ -25902,37 +25902,37 @@
       </c>
       <c r="C34" s="30" t="inlineStr">
         <is>
-          <t>17098963</t>
+          <t>17133115</t>
         </is>
       </c>
       <c r="D34" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>412 - COHAB</t>
         </is>
       </c>
       <c r="E34" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="F34" s="29" t="inlineStr">
         <is>
-          <t>Rua ARINO MOREIRA</t>
+          <t>Rua VALENCIO DE BRUM</t>
         </is>
       </c>
       <c r="G34" s="29" t="inlineStr">
         <is>
-          <t>39 - R</t>
+          <t>536 - R</t>
         </is>
       </c>
       <c r="H34" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:46</t>
+          <t>25/08/2026 09:33</t>
         </is>
       </c>
       <c r="I34" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 16:03</t>
+          <t>25/08/2026 09:50</t>
         </is>
       </c>
       <c r="J34" s="29" t="n">
@@ -25942,7 +25942,7 @@
     <row r="35">
       <c r="A35" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B35" s="29" t="inlineStr">
@@ -25952,37 +25952,37 @@
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>17195900</t>
+          <t>17184338</t>
         </is>
       </c>
       <c r="D35" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E35" s="29" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="F35" s="29" t="inlineStr">
         <is>
-          <t>Rua 13 DE SETEMBRO</t>
+          <t>Rua GENERAL OSORIO</t>
         </is>
       </c>
       <c r="G35" s="29" t="inlineStr">
         <is>
-          <t>1502 - R</t>
+          <t>1353 - C</t>
         </is>
       </c>
       <c r="H35" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:53</t>
+          <t>27/08/2026 13:50</t>
         </is>
       </c>
       <c r="I35" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 15:10</t>
+          <t>27/08/2026 14:07</t>
         </is>
       </c>
       <c r="J35" s="29" t="n">
@@ -25992,47 +25992,47 @@
     <row r="36">
       <c r="A36" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="B36" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C36" s="30" t="inlineStr">
         <is>
-          <t>17098958</t>
+          <t>17137370</t>
         </is>
       </c>
       <c r="D36" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>402 - JARDIM MARAMBAIA</t>
         </is>
       </c>
       <c r="E36" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F36" s="29" t="inlineStr">
         <is>
-          <t>Avenida COMANDANTE CARDOSO</t>
+          <t>Rua DR HELIO BRANDAO</t>
         </is>
       </c>
       <c r="G36" s="29" t="inlineStr">
         <is>
-          <t>258 - 2 - OU</t>
+          <t>647 - R</t>
         </is>
       </c>
       <c r="H36" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 14:47</t>
+          <t>25/08/2026 16:03</t>
         </is>
       </c>
       <c r="I36" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:03</t>
+          <t>25/08/2026 16:19</t>
         </is>
       </c>
       <c r="J36" s="29" t="n">
@@ -26192,47 +26192,47 @@
     <row r="40">
       <c r="A40" s="29" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B40" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C40" s="30" t="inlineStr">
         <is>
-          <t>17137370</t>
+          <t>17098958</t>
         </is>
       </c>
       <c r="D40" s="29" t="inlineStr">
         <is>
-          <t>402 - JARDIM MARAMBAIA</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E40" s="29" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F40" s="29" t="inlineStr">
         <is>
-          <t>Rua DR HELIO BRANDAO</t>
+          <t>Avenida COMANDANTE CARDOSO</t>
         </is>
       </c>
       <c r="G40" s="29" t="inlineStr">
         <is>
-          <t>647 - R</t>
+          <t>258 - 2 - OU</t>
         </is>
       </c>
       <c r="H40" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 16:03</t>
+          <t>24/08/2026 14:47</t>
         </is>
       </c>
       <c r="I40" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 16:19</t>
+          <t>24/08/2026 15:03</t>
         </is>
       </c>
       <c r="J40" s="29" t="n">
